--- a/OrderbookAutomation/output/Workbook_Profile.xlsx
+++ b/OrderbookAutomation/output/Workbook_Profile.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,7 +492,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mat_Desc,_MOQ_,_Material_#.xlsx</t>
+          <t>MOQ.xlsx</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -672,7 +672,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -681,51 +681,21 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="E9" t="n">
-        <v>1427</v>
+        <v>322304</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>101</v>
-      </c>
-      <c r="D10" t="n">
-        <v>66</v>
-      </c>
-      <c r="E10" t="n">
-        <v>322304</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -740,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1889,7 +1859,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mat_Desc,_MOQ_,_Material_#.xlsx</t>
+          <t>MOQ.xlsx</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1922,7 +1892,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mat_Desc,_MOQ_,_Material_#.xlsx</t>
+          <t>MOQ.xlsx</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1955,7 +1925,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Mat_Desc,_MOQ_,_Material_#.xlsx</t>
+          <t>MOQ.xlsx</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1988,7 +1958,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mat_Desc,_MOQ_,_Material_#.xlsx</t>
+          <t>MOQ.xlsx</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3568,7 +3538,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3578,7 +3548,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sales Order No.</t>
+          <t>NDC Code</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3590,18 +3560,18 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>3612002936</t>
+          <t>64380020101</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3611,30 +3581,30 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Item No.</t>
+          <t>Material Description</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>AMLO/HCTZ/VALSAR TAB 10/25/320 MG 30</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3644,7 +3614,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lookup</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3656,18 +3626,18 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>64380020101EXPRESS SCRIPTS</t>
+          <t>AVH</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3677,8 +3647,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Matl._x000d_
-Code</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3690,18 +3659,18 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>3011903</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3711,30 +3680,30 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NDC Code</t>
+          <t>SPI/CR</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>64380020101</t>
+          <t>CR</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3744,7 +3713,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Material Description</t>
+          <t>Sold-to party Name</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3756,18 +3725,18 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>AMLO/HCTZ/VALSAR TAB 10/25/320 MG 30</t>
+          <t>CENCORA GLOBAL PROCUREMENT</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3777,8 +3746,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Total Stock _x000d_
-In-hand</t>
+          <t>Cust Group</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3790,18 +3758,18 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>23,061</t>
+          <t>WBAD</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3811,7 +3779,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>UPS Inventory</t>
+          <t xml:space="preserve"> Cont ID </t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3823,18 +3791,18 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>21,696</t>
+          <t>ABCS0614</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3844,30 +3812,30 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pack Size (MOQ)</t>
+          <t>x</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>64380020101CENCORA GLOBAL PROCUREMENT</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3877,30 +3845,30 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sales Order Qty</t>
+          <t xml:space="preserve"> Jul-22 </t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve"> -   </t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3910,30 +3878,30 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sales Qty MTD</t>
+          <t xml:space="preserve"> Aug-22 </t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve"> 336 </t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3943,30 +3911,30 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Forecast Qty</t>
+          <t xml:space="preserve"> Sep-22 </t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>366</t>
+          <t xml:space="preserve"> 1,056 </t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3976,30 +3944,30 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sold-to party</t>
+          <t xml:space="preserve"> Oct-22 </t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>9700306</t>
+          <t xml:space="preserve"> 696 </t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4009,7 +3977,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sold-to party Name</t>
+          <t xml:space="preserve"> Nov-22 </t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4018,21 +3986,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>EXPRESS SCRIPTS</t>
+          <t xml:space="preserve"> 360 </t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4042,26 +4010,30 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t xml:space="preserve"> Dec-22 </t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 864 </t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4071,7 +4043,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>S.O. Type</t>
+          <t xml:space="preserve"> Jan-23 </t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4080,21 +4052,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ZTRU</t>
+          <t xml:space="preserve"> 1,104 </t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4104,30 +4076,30 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Unit Price </t>
+          <t xml:space="preserve"> Feb-23 </t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>160.06</t>
+          <t xml:space="preserve"> 1,152 </t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4137,7 +4109,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sales Value (FC) </t>
+          <t xml:space="preserve"> Mar-23 </t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4146,21 +4118,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>11,524.32</t>
+          <t xml:space="preserve"> 1,200 </t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4170,30 +4142,30 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>WAC/BG price in EDI</t>
+          <t xml:space="preserve"> Apr-23 </t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>160.06</t>
+          <t xml:space="preserve"> 1,200 </t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4203,7 +4175,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PO Number</t>
+          <t xml:space="preserve"> May-23 </t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4212,21 +4184,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1036729-2331</t>
+          <t xml:space="preserve"> 1,440 </t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4236,7 +4208,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PO Date</t>
+          <t xml:space="preserve"> June-23 </t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4245,21 +4217,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>7/28/26</t>
+          <t xml:space="preserve"> 1,488 </t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4269,30 +4241,30 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ship-to party</t>
+          <t xml:space="preserve"> Jul-23 </t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F108" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>9800112</t>
+          <t xml:space="preserve"> 1,032 </t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4302,7 +4274,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ship-to party Name</t>
+          <t xml:space="preserve"> Aug-23 </t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4311,21 +4283,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F109" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>EXPRESS SCRIPTS_BURLINGTON</t>
+          <t xml:space="preserve"> 1,344 </t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4335,7 +4307,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t xml:space="preserve"> Sept-23 </t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4344,21 +4316,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2040 ROUTE 130 NORTH</t>
+          <t xml:space="preserve"> 1,440 </t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4368,7 +4340,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>City</t>
+          <t xml:space="preserve"> Oct-23 </t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4377,21 +4349,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>BURLINGTON</t>
+          <t xml:space="preserve"> 1,368 </t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4401,7 +4373,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t xml:space="preserve"> Nov-23 </t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4410,21 +4382,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t xml:space="preserve"> 1,512 </t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4434,30 +4406,30 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Postal Code</t>
+          <t xml:space="preserve"> Dec-23 </t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t xml:space="preserve"> 1,200 </t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4467,7 +4439,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t xml:space="preserve"> Jan-24 </t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4476,21 +4448,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>US</t>
+          <t xml:space="preserve"> 1,560 </t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4500,7 +4472,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Reas. Rej.</t>
+          <t xml:space="preserve"> Feb-24 </t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4509,21 +4481,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Y6</t>
+          <t xml:space="preserve"> 1,368 </t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4533,7 +4505,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Reason for Rejection</t>
+          <t xml:space="preserve"> Mar-24 </t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4542,21 +4514,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>ZUS Y6 Block</t>
+          <t xml:space="preserve"> 1,776 </t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4566,7 +4538,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Material Blk</t>
+          <t xml:space="preserve"> Apr-24 </t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4575,21 +4547,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>X</t>
+          <t xml:space="preserve"> 1,848 </t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4599,26 +4571,30 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Floor limit Blk</t>
+          <t xml:space="preserve"> May-24 </t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2,064 </t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4628,26 +4604,30 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Multiple of MOQ Blk</t>
+          <t xml:space="preserve"> June-24 </t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,152 </t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4657,26 +4637,30 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Expected Price Blk</t>
+          <t xml:space="preserve"> July-24 </t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,488 </t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4686,7 +4670,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DEA Number (Customer Master)</t>
+          <t xml:space="preserve"> Aug-24 </t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4695,21 +4679,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>FE4492738</t>
+          <t xml:space="preserve"> 2,160 </t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4719,7 +4703,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Req. Delivery Date</t>
+          <t xml:space="preserve"> Sept-24 </t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4728,21 +4712,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F122" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>7/28/26</t>
+          <t xml:space="preserve"> 1,680 </t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>sales_summ.xlsx</t>
+          <t>Strend.xlsx</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4752,21 +4736,25 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SOM Indc.</t>
+          <t xml:space="preserve"> Oct-24 </t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>float64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1,896 </t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4781,23 +4769,23 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NDC Code</t>
+          <t xml:space="preserve"> Nov-24 </t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F124" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>64380020101</t>
+          <t xml:space="preserve"> 1,632 </t>
         </is>
       </c>
     </row>
@@ -4814,7 +4802,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Material Description</t>
+          <t xml:space="preserve"> Dec 2024 </t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4823,14 +4811,14 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F125" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>AMLO/HCTZ/VALSAR TAB 10/25/320 MG 30</t>
+          <t xml:space="preserve"> 2,928 </t>
         </is>
       </c>
     </row>
@@ -4847,7 +4835,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t xml:space="preserve"> Jan-25 </t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4856,14 +4844,14 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F126" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>AVH</t>
+          <t xml:space="preserve"> 1,464 </t>
         </is>
       </c>
     </row>
@@ -4880,23 +4868,23 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t xml:space="preserve"> Feb-25 </t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>int64</t>
+          <t>str</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F127" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve"> 2,472 </t>
         </is>
       </c>
     </row>
@@ -4913,7 +4901,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SPI/CR</t>
+          <t xml:space="preserve"> Mar-25 </t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4922,14 +4910,14 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t xml:space="preserve"> 1,344 </t>
         </is>
       </c>
     </row>
@@ -4946,7 +4934,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sold-to party Name</t>
+          <t xml:space="preserve"> Apr-25 </t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4955,14 +4943,14 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F129" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>CENCORA GLOBAL PROCUREMENT</t>
+          <t xml:space="preserve"> -   </t>
         </is>
       </c>
     </row>
@@ -4979,7 +4967,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Cust Group</t>
+          <t xml:space="preserve"> May 25 </t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4988,14 +4976,14 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F130" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>WBAD</t>
+          <t xml:space="preserve"> 1,920 </t>
         </is>
       </c>
     </row>
@@ -5012,7 +5000,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Cont ID </t>
+          <t xml:space="preserve"> June-25 </t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -5021,14 +5009,14 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F131" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>ABCS0614</t>
+          <t xml:space="preserve"> 2,520 </t>
         </is>
       </c>
     </row>
@@ -5045,7 +5033,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>x</t>
+          <t xml:space="preserve"> July-25 </t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5054,14 +5042,14 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F132" t="n">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>64380020101CENCORA GLOBAL PROCUREMENT</t>
+          <t xml:space="preserve"> 1,032 </t>
         </is>
       </c>
     </row>
@@ -5078,7 +5066,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jul-22 </t>
+          <t xml:space="preserve"> Aug-25 </t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5087,14 +5075,14 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="F133" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve"> -   </t>
+          <t xml:space="preserve"> 48 </t>
         </is>
       </c>
     </row>
@@ -5111,7 +5099,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Aug-22 </t>
+          <t xml:space="preserve"> Sept-25 </t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -5120,14 +5108,14 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F134" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 336 </t>
+          <t xml:space="preserve"> -   </t>
         </is>
       </c>
     </row>
@@ -5144,7 +5132,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sep-22 </t>
+          <t xml:space="preserve"> Oct-25 </t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -5153,14 +5141,14 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F135" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,056 </t>
+          <t xml:space="preserve"> -   </t>
         </is>
       </c>
     </row>
@@ -5177,7 +5165,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Oct-22 </t>
+          <t xml:space="preserve"> Nov-25 </t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -5186,14 +5174,14 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F136" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 696 </t>
+          <t xml:space="preserve"> 576 </t>
         </is>
       </c>
     </row>
@@ -5210,7 +5198,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Nov-22 </t>
+          <t xml:space="preserve"> Dec-25 </t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -5219,14 +5207,14 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="F137" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 360 </t>
+          <t xml:space="preserve"> 120 </t>
         </is>
       </c>
     </row>
@@ -5243,7 +5231,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dec-22 </t>
+          <t xml:space="preserve"> Jan-26 </t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -5252,14 +5240,14 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="F138" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 864 </t>
+          <t xml:space="preserve"> 120 </t>
         </is>
       </c>
     </row>
@@ -5276,7 +5264,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jan-23 </t>
+          <t xml:space="preserve"> Feb-26 </t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5285,14 +5273,14 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F139" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,104 </t>
+          <t xml:space="preserve"> 504 </t>
         </is>
       </c>
     </row>
@@ -5309,7 +5297,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feb-23 </t>
+          <t xml:space="preserve"> Mar-26 </t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5318,14 +5306,14 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="F140" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,152 </t>
+          <t xml:space="preserve"> 240 </t>
         </is>
       </c>
     </row>
@@ -5342,7 +5330,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Mar-23 </t>
+          <t xml:space="preserve"> Apr-26 </t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -5351,14 +5339,14 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="F141" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,200 </t>
+          <t xml:space="preserve"> 240 </t>
         </is>
       </c>
     </row>
@@ -5375,7 +5363,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Apr-23 </t>
+          <t xml:space="preserve"> May-26 </t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5384,14 +5372,14 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="F142" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,200 </t>
+          <t xml:space="preserve"> 48 </t>
         </is>
       </c>
     </row>
@@ -5408,7 +5396,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> May-23 </t>
+          <t xml:space="preserve"> June-26 </t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5417,14 +5405,14 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F143" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,440 </t>
+          <t xml:space="preserve"> 168 </t>
         </is>
       </c>
     </row>
@@ -5441,7 +5429,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> June-23 </t>
+          <t xml:space="preserve"> Jul-26 </t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5450,14 +5438,14 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,488 </t>
+          <t xml:space="preserve"> 144 </t>
         </is>
       </c>
     </row>
@@ -5474,7 +5462,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jul-23 </t>
+          <t xml:space="preserve"> Open Order 7-29-2026 </t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5483,14 +5471,14 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,032 </t>
+          <t xml:space="preserve"> 96 </t>
         </is>
       </c>
     </row>
@@ -5507,7 +5495,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Aug-23 </t>
+          <t xml:space="preserve"> Released Order 7-29-2026 </t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5516,14 +5504,14 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,344 </t>
+          <t xml:space="preserve"> -   </t>
         </is>
       </c>
     </row>
@@ -5540,7 +5528,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Sept-23 </t>
+          <t xml:space="preserve"> Pending invoice-SAP 7-29-2026 </t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5549,14 +5537,14 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,440 </t>
+          <t xml:space="preserve"> 72 </t>
         </is>
       </c>
     </row>
@@ -5573,7 +5561,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Oct-23 </t>
+          <t xml:space="preserve"> July -26 </t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5582,14 +5570,14 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,368 </t>
+          <t xml:space="preserve"> 312 </t>
         </is>
       </c>
     </row>
@@ -5606,7 +5594,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Nov-23 </t>
+          <t xml:space="preserve"> July'26- Forecast </t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5615,14 +5603,14 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="F149" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,512 </t>
+          <t xml:space="preserve"> 250 </t>
         </is>
       </c>
     </row>
@@ -5639,7 +5627,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Dec-23 </t>
+          <t xml:space="preserve"> Avg Jan'26 to June'26 </t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5648,14 +5636,14 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="F150" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,200 </t>
+          <t xml:space="preserve"> 220 </t>
         </is>
       </c>
     </row>
@@ -5672,7 +5660,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Jan-24 </t>
+          <t xml:space="preserve"> % </t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5681,14 +5669,14 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1,560 </t>
+          <t>65%</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5693,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Feb-24 </t>
+          <t xml:space="preserve"> MTD-Target </t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5714,1233 +5702,12 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="F152" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="G152" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 1,368 </t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Mar-24 </t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E153" t="n">
-        <v>45</v>
-      </c>
-      <c r="F153" t="n">
-        <v>19</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 1,776 </t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Apr-24 </t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E154" t="n">
-        <v>45</v>
-      </c>
-      <c r="F154" t="n">
-        <v>14</v>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 1,848 </t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> May-24 </t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E155" t="n">
-        <v>44</v>
-      </c>
-      <c r="F155" t="n">
-        <v>18</v>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 2,064 </t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> June-24 </t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E156" t="n">
-        <v>39</v>
-      </c>
-      <c r="F156" t="n">
-        <v>16</v>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 1,152 </t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> July-24 </t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E157" t="n">
-        <v>36</v>
-      </c>
-      <c r="F157" t="n">
-        <v>16</v>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 1,488 </t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Aug-24 </t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E158" t="n">
-        <v>35</v>
-      </c>
-      <c r="F158" t="n">
-        <v>15</v>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 2,160 </t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Sept-24 </t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E159" t="n">
-        <v>35</v>
-      </c>
-      <c r="F159" t="n">
-        <v>16</v>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 1,680 </t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Oct-24 </t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E160" t="n">
-        <v>34</v>
-      </c>
-      <c r="F160" t="n">
-        <v>17</v>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 1,896 </t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Nov-24 </t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
-        <v>33</v>
-      </c>
-      <c r="F161" t="n">
-        <v>15</v>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 1,632 </t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Dec 2024 </t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E162" t="n">
-        <v>33</v>
-      </c>
-      <c r="F162" t="n">
-        <v>20</v>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 2,928 </t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Jan-25 </t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E163" t="n">
-        <v>33</v>
-      </c>
-      <c r="F163" t="n">
-        <v>14</v>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 1,464 </t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Feb-25 </t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E164" t="n">
-        <v>32</v>
-      </c>
-      <c r="F164" t="n">
-        <v>15</v>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 2,472 </t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Mar-25 </t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E165" t="n">
-        <v>32</v>
-      </c>
-      <c r="F165" t="n">
-        <v>20</v>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 1,344 </t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Apr-25 </t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E166" t="n">
-        <v>31</v>
-      </c>
-      <c r="F166" t="n">
-        <v>18</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> -   </t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> May 25 </t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E167" t="n">
-        <v>31</v>
-      </c>
-      <c r="F167" t="n">
-        <v>20</v>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 1,920 </t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> June-25 </t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E168" t="n">
-        <v>30</v>
-      </c>
-      <c r="F168" t="n">
-        <v>20</v>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 2,520 </t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> July-25 </t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E169" t="n">
-        <v>26</v>
-      </c>
-      <c r="F169" t="n">
-        <v>18</v>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 1,032 </t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Aug-25 </t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E170" t="n">
-        <v>25</v>
-      </c>
-      <c r="F170" t="n">
-        <v>14</v>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 48 </t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Sept-25 </t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E171" t="n">
-        <v>20</v>
-      </c>
-      <c r="F171" t="n">
-        <v>20</v>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> -   </t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Oct-25 </t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E172" t="n">
-        <v>18</v>
-      </c>
-      <c r="F172" t="n">
-        <v>16</v>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> -   </t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Nov-25 </t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E173" t="n">
-        <v>16</v>
-      </c>
-      <c r="F173" t="n">
-        <v>20</v>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 576 </t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Dec-25 </t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E174" t="n">
-        <v>15</v>
-      </c>
-      <c r="F174" t="n">
-        <v>22</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 120 </t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Jan-26 </t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E175" t="n">
-        <v>14</v>
-      </c>
-      <c r="F175" t="n">
-        <v>18</v>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 120 </t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Feb-26 </t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E176" t="n">
-        <v>12</v>
-      </c>
-      <c r="F176" t="n">
-        <v>21</v>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 504 </t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Mar-26 </t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E177" t="n">
-        <v>9</v>
-      </c>
-      <c r="F177" t="n">
-        <v>22</v>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 240 </t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Apr-26 </t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E178" t="n">
-        <v>6</v>
-      </c>
-      <c r="F178" t="n">
-        <v>20</v>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 240 </t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> May-26 </t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E179" t="n">
-        <v>6</v>
-      </c>
-      <c r="F179" t="n">
-        <v>16</v>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 48 </t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> June-26 </t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E180" t="n">
-        <v>4</v>
-      </c>
-      <c r="F180" t="n">
-        <v>22</v>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 168 </t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Jul-26 </t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E181" t="n">
-        <v>0</v>
-      </c>
-      <c r="F181" t="n">
-        <v>16</v>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 144 </t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Open Order 7-29-2026 </t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E182" t="n">
-        <v>0</v>
-      </c>
-      <c r="F182" t="n">
-        <v>6</v>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 96 </t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Released Order 7-29-2026 </t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E183" t="n">
-        <v>0</v>
-      </c>
-      <c r="F183" t="n">
-        <v>3</v>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> -   </t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Pending invoice-SAP 7-29-2026 </t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E184" t="n">
-        <v>0</v>
-      </c>
-      <c r="F184" t="n">
-        <v>6</v>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 72 </t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> July -26 </t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E185" t="n">
-        <v>0</v>
-      </c>
-      <c r="F185" t="n">
-        <v>20</v>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 312 </t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> July'26- Forecast </t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E186" t="n">
-        <v>3</v>
-      </c>
-      <c r="F186" t="n">
-        <v>50</v>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 250 </t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Avg Jan'26 to June'26 </t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E187" t="n">
-        <v>1</v>
-      </c>
-      <c r="F187" t="n">
-        <v>41</v>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 220 </t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> % </t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E188" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" t="n">
-        <v>23</v>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Strend.xlsx</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> MTD-Target </t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E189" t="n">
-        <v>1</v>
-      </c>
-      <c r="F189" t="n">
-        <v>41</v>
-      </c>
-      <c r="G189" t="inlineStr">
         <is>
           <t xml:space="preserve"> 220 </t>
         </is>
